--- a/product-definitions/spreadsheet/oh-concentration.xlsx
+++ b/product-definitions/spreadsheet/oh-concentration.xlsx
@@ -144,7 +144,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -174,11 +174,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -233,7 +228,7 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -1802,7 +1797,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
         <v>19</v>
@@ -1811,7 +1806,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
         <v>21</v>
@@ -1820,7 +1815,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="11" t="s">
         <v>22</v>
@@ -1831,7 +1826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
         <v>24</v>
@@ -1840,19 +1835,19 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="8"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="7"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
         <v>10</v>
@@ -1861,7 +1856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
         <v>12</v>
@@ -1870,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
         <v>2</v>
@@ -1879,7 +1874,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -1889,7 +1884,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -1898,7 +1893,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
         <v>18</v>
@@ -1907,7 +1902,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
         <v>19</v>
@@ -1916,7 +1911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
         <v>21</v>
@@ -1925,7 +1920,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="11" t="s">
         <v>22</v>
@@ -1936,7 +1931,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
         <v>24</v>
@@ -1945,19 +1940,19 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="8"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="7"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
         <v>10</v>
@@ -1966,7 +1961,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
         <v>12</v>
@@ -1975,7 +1970,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
         <v>2</v>
@@ -1984,7 +1979,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -1994,7 +1989,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2003,7 +1998,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
         <v>18</v>
@@ -2012,7 +2007,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
         <v>19</v>
@@ -2021,7 +2016,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
         <v>21</v>
@@ -2030,7 +2025,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="11" t="s">
         <v>22</v>
@@ -2041,7 +2036,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
         <v>24</v>
@@ -2050,19 +2045,19 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="8"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="8"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
         <v>10</v>
@@ -2071,7 +2066,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
         <v>12</v>
@@ -2080,7 +2075,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
         <v>2</v>
@@ -2089,14 +2084,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="8"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="2"/>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -2105,7 +2100,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="14" t="s">
         <v>37</v>
@@ -2119,7 +2114,7 @@
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="12" t="s">
         <v>39</v>
